--- a/data/incremental/incremental_09_chillan_manual.xlsx
+++ b/data/incremental/incremental_09_chillan_manual.xlsx
@@ -10,7 +10,7 @@
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="Restaurantes" sheetId="1" state="visible" r:id="rId1"/>
   </sheets>
   <definedNames>
-    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$26</definedName>
+    <definedName name="_xlnm._FilterDatabase" localSheetId="0" hidden="1">'Restaurantes'!$A$1:$AG$31</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AG26"/>
+  <dimension ref="A1:AG31"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="42" customWidth="1" min="1" max="1"/>
@@ -460,7 +460,7 @@
     <col width="15" customWidth="1" min="30" max="30"/>
     <col width="12" customWidth="1" min="31" max="31"/>
     <col width="17" customWidth="1" min="32" max="32"/>
-    <col width="26" customWidth="1" min="33" max="33"/>
+    <col width="22" customWidth="1" min="33" max="33"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -668,7 +668,7 @@
       </c>
       <c r="H2" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casa+del+Barrio/@-36.5789187,-72.0512433,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d741f1e7bf11:0xbdbf15c689318ef0!8m2!3d-36.5789187!4d-72.0512433!16s%2Fg%2F11lss72rjz?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Casa+del+Barrio/data=!4m7!3m6!1s0x9668d741f1e7bf11:0xbdbf15c689318ef0!8m2!3d-36.5789187!4d-72.0512433!16s%2Fg%2F11lss72rjz!19sChIJEb_n8UHXaJYR8I4xicYVv70?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I2" t="inlineStr">
@@ -703,7 +703,7 @@
       </c>
       <c r="O2" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P2" t="inlineStr">
@@ -771,7 +771,7 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Onde'l+Pala/@-36.6007129,-72.0955085,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d7d32357ba4b:0xcbd450cc8b813db6!8m2!3d-36.6007129!4d-72.0955085!16s%2Fg%2F11clhq9lvn?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Onde%27l+Pala/data=!4m7!3m6!1s0x9668d7d32357ba4b:0xcbd450cc8b813db6!8m2!3d-36.6007129!4d-72.0955085!16s%2Fg%2F11clhq9lvn!19sChIJS7pXI9PXaJYRtj2Bi8xQ1Ms?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
@@ -806,7 +806,7 @@
       </c>
       <c r="O3" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P3" t="inlineStr">
@@ -839,30 +839,34 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>Restaurante La Caleta De Tito</t>
+          <t>Secretos de la Nona Chillán Casa Matriz Tienda 1</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>472</t>
+          <t>717</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>Av. Argentina 747, Chillán, Ñuble</t>
+          <t>Arauco 937, 3800926 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
         <is>
-          <t>(42) 238 4858</t>
-        </is>
-      </c>
-      <c r="F4" t="inlineStr"/>
+          <t>9 8573 2009</t>
+        </is>
+      </c>
+      <c r="F4" t="inlineStr">
+        <is>
+          <t>https://secretosdelanona.cl/</t>
+        </is>
+      </c>
       <c r="G4" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -870,17 +874,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+La+Caleta+De+Tito/data=!4m7!3m6!1s0x966929d4b24978ff:0x56054506a338f247!8m2!3d-36.6117125!4d-72.0939595!16s%2Fg%2F11f03x99wf!19sChIJ_3hJstQpaZYRR_I4owZFBVY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Secretos+de+la+Nona+Chill%C3%A1n+Casa+Matriz+Tienda+1/data=!4m7!3m6!1s0x96692828f5997465:0x8416716d711296f7!8m2!3d-36.6116984!4d-72.1043029!16s%2Fg%2F11bwqg83gz!19sChIJZXSZ9SgoaZYR95YScW1xFoQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-36.6117125</t>
+          <t>-36.6116984</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-72.0939595</t>
+          <t>-72.1043029</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -905,12 +909,12 @@
       </c>
       <c r="O4" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P4" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q4" t="inlineStr">
@@ -938,7 +942,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Aay Chabela Restaurant</t>
+          <t>Brote de Primavera</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -948,24 +952,20 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>847</t>
+          <t>140</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>Arauco 660, 3780000 Chillán, Ñuble</t>
+          <t>Arturo Prat 415, 3780000 Chillán, Bío Bío</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
         <is>
-          <t>9 3503 9550</t>
-        </is>
-      </c>
-      <c r="F5" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/aychabelarestaurant/</t>
-        </is>
-      </c>
+          <t>9 4855 5636</t>
+        </is>
+      </c>
+      <c r="F5" t="inlineStr"/>
       <c r="G5" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -973,17 +973,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Aay+Chabela+Restaurant/data=!4m7!3m6!1s0x9668d7dea8c4930b:0x2770903794774fc5!8m2!3d-36.6081967!4d-72.1033385!16s%2Fg%2F11f5v7km71!19sChIJC5PEqN7XaJYRxU93lDeQcCc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Brote+de+Primavera/data=!4m7!3m6!1s0x9668d743b1787749:0x74379625a16cd3fe!8m2!3d-36.610358!4d-72.1070076!16s%2Fg%2F11qyc3f_dy!19sChIJSXd4sUPXaJYR_tNsoSWWN3Q?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-36.6081967</t>
+          <t>-36.610358</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-72.1033385</t>
+          <t>-72.1070076</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -1008,12 +1008,12 @@
       </c>
       <c r="O5" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P5" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q5" t="inlineStr">
@@ -1041,48 +1041,52 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>Restaurante 3 Regiones</t>
+          <t>Fuego Di Vino</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>279</t>
+          <t>667</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>Av. Argentina 431, 3820572 Chillán, Ñuble</t>
+          <t>Gamero 980, 3800623 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
         <is>
-          <t>9 6417 7736</t>
-        </is>
-      </c>
-      <c r="F6" t="inlineStr"/>
+          <t>(42) 243 0900</t>
+        </is>
+      </c>
+      <c r="F6" t="inlineStr">
+        <is>
+          <t>http://www.fuegodivino.cl/</t>
+        </is>
+      </c>
       <c r="G6" t="inlineStr">
         <is>
-          <t>Restaurante peruano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+3+Regiones/@-36.6078265,-72.092205,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d757623c17bb:0xf348bc1a5fa133b8!8m2!3d-36.6078265!4d-72.092205!16s%2Fg%2F11qbr9886l?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Fuego+Di+Vino/data=!4m7!3m6!1s0x9668d7d4d0353efb:0x5a23baae07b4f345!8m2!3d-36.6041503!4d-72.0951384!16s%2Fg%2F11b7q5qwbg!19sChIJ-z410NTXaJYRRfO0B666I1o?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-36.6078265</t>
+          <t>-36.6041503</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-72.092205</t>
+          <t>-72.0951384</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -1107,12 +1111,12 @@
       </c>
       <c r="O6" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P6" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q6" t="inlineStr">
@@ -1140,7 +1144,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>Restaurant La Abuelita</t>
+          <t>Restaurant Zasha</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -1150,20 +1154,24 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>433</t>
+          <t>08</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>Flores Millán 1093, 3800061 Chillán, Ñuble</t>
+          <t>Av. Libertad 802, 3780000 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
         <is>
-          <t>(42) 225 3956</t>
-        </is>
-      </c>
-      <c r="F7" t="inlineStr"/>
+          <t>9 9051 4742</t>
+        </is>
+      </c>
+      <c r="F7" t="inlineStr">
+        <is>
+          <t>https://zasha.cl/carta/</t>
+        </is>
+      </c>
       <c r="G7" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1171,17 +1179,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+La+Abuelita/data=!4m7!3m6!1s0x9668d79c79fa8b8d:0xee00d9ad405dd3bc!8m2!3d-36.5906248!4d-72.087245!16s%2Fg%2F11spps83kt!19sChIJjYv6eZzXaJYRvNNdQK3ZAO4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurant+Zasha/data=!4m7!3m6!1s0x9668d7d5eec972b7:0xfb0866f2c16242a9!8m2!3d-36.6072718!4d-72.0992526!16s%2Fg%2F11f54mczxm!19sChIJt3LJ7tXXaJYRqUJiwfJmCPs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-36.5906248</t>
+          <t>-36.6072718</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-72.087245</t>
+          <t>-72.0992526</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -1206,12 +1214,12 @@
       </c>
       <c r="O7" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P7" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q7" t="inlineStr">
@@ -1239,34 +1247,30 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>Vita Wines House, Casa de vinos</t>
+          <t>Restaurante La Caleta De Tito</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>4.8</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>93</t>
+          <t>472</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>Los Mallines 208, 3800146 Chillán, Ñuble</t>
+          <t>Av. Argentina 747, Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
         <is>
-          <t>9 9933 2606</t>
-        </is>
-      </c>
-      <c r="F8" t="inlineStr">
-        <is>
-          <t>https://vitawines.cl/</t>
-        </is>
-      </c>
+          <t>(42) 238 4858</t>
+        </is>
+      </c>
+      <c r="F8" t="inlineStr"/>
       <c r="G8" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1274,17 +1278,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Vita+Wines+House,+Casa+de+vinos/@-36.5928329,-72.1037306,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d786459af0b9:0xff81c3a3610f9d43!8m2!3d-36.5928329!4d-72.1037306!16s%2Fg%2F11k9zc5rwv?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+La+Caleta+De+Tito/data=!4m7!3m6!1s0x966929d4b24978ff:0x56054506a338f247!8m2!3d-36.6117125!4d-72.0939595!16s%2Fg%2F11f03x99wf!19sChIJ_3hJstQpaZYRR_I4owZFBVY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-36.5928329</t>
+          <t>-36.6117125</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-72.1037306</t>
+          <t>-72.0939595</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -1309,12 +1313,12 @@
       </c>
       <c r="O8" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P8" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q8" t="inlineStr">
@@ -1342,27 +1346,27 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>Restaurante "Rocas"</t>
+          <t>Restaurante Pensión Valdés</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>Av. Libertad 684, Chillán, Ñuble</t>
+          <t>Maipón 897, Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
         <is>
-          <t>9 4188 5321</t>
+          <t>(42) 222 4312</t>
         </is>
       </c>
       <c r="F9" t="inlineStr"/>
@@ -1373,17 +1377,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+%22Rocas%22/data=!4m7!3m6!1s0x9668d779cbadee3f:0x7c331be78e0b9dd1!8m2!3d-36.6067519!4d-72.1011348!16s%2Fg%2F11h2jmqsjv!19sChIJP-6ty3nXaJYR0Z0LjucbM3w?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+Pensi%C3%B3n+Vald%C3%A9s/data=!4m7!3m6!1s0x9669282bcd0e6601:0x12c9f5813e7913c7!8m2!3d-36.6109309!4d-72.0992906!16s%2Fg%2F11b8_y25r6!19sChIJAWYOzSsoaZYRxxN5PoH1yRI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-36.6067519</t>
+          <t>-36.6109309</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-72.1011348</t>
+          <t>-72.0992906</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -1408,7 +1412,7 @@
       </c>
       <c r="O9" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P9" t="inlineStr">
@@ -1441,32 +1445,32 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>Volcano Restaurant</t>
+          <t>Aay Chabela Restaurant</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.7</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>184</t>
+          <t>849</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>Casino marina del sol - Variante Nahueltoro 251, local 2, 3820572 Chillán, Ñuble</t>
+          <t>Arauco 660, 3780000 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
         <is>
-          <t>9 5827 1755</t>
+          <t>9 3503 9550</t>
         </is>
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>http://www.volcanorestaurant.cl/</t>
+          <t>https://www.facebook.com/aychabelarestaurant/</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -1476,17 +1480,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Volcano+Restaurant/data=!4m7!3m6!1s0x9668d7ba06c77f91:0x6f3eb74ac17461d!8m2!3d-36.5609654!4d-72.0933011!16s%2Fg%2F11k56967tb!19sChIJkX_HBrrXaJYRHUYXrHTr8wY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Aay+Chabela+Restaurant/data=!4m7!3m6!1s0x9668d7dea8c4930b:0x2770903794774fc5!8m2!3d-36.6081967!4d-72.1033385!16s%2Fg%2F11f5v7km71!19sChIJC5PEqN7XaJYRxU93lDeQcCc?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-36.5609654</t>
+          <t>-36.6081967</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-72.0933011</t>
+          <t>-72.1033385</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -1511,7 +1515,7 @@
       </c>
       <c r="O10" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P10" t="inlineStr">
@@ -1544,27 +1548,27 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>Restaurant El Chapu</t>
+          <t>Restaurant La Abuelita</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>822</t>
+          <t>433</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>Las Rosas 641, Chillán, Biobío</t>
+          <t>Flores Millán 1093, 3800061 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
         <is>
-          <t>9 9711 3623</t>
+          <t>(42) 225 3956</t>
         </is>
       </c>
       <c r="F11" t="inlineStr"/>
@@ -1575,17 +1579,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+El+Chapu/@-36.611892,-72.0821374,17z/data=!3m1!4b1!4m6!3m5!1s0x9669ca19b111c019:0x70fd64e57055940c!8m2!3d-36.611892!4d-72.0821374!16s%2Fg%2F1tgwc36w?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurant+La+Abuelita/data=!4m7!3m6!1s0x9668d79c79fa8b8d:0xee00d9ad405dd3bc!8m2!3d-36.5906248!4d-72.087245!16s%2Fg%2F11spps83kt!19sChIJjYv6eZzXaJYRvNNdQK3ZAO4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-36.611892</t>
+          <t>-36.5906248</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-72.0821374</t>
+          <t>-72.087245</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -1610,7 +1614,7 @@
       </c>
       <c r="O11" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P11" t="inlineStr">
@@ -1643,52 +1647,48 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>Restaurant Zasha</t>
+          <t>Restaurante 3 Regiones</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>08</t>
+          <t>279</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>Av. Libertad 802, 3780000 Chillán, Ñuble</t>
+          <t>Av. Argentina 431, 3820572 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
         <is>
-          <t>9 9051 4742</t>
-        </is>
-      </c>
-      <c r="F12" t="inlineStr">
-        <is>
-          <t>https://zasha.cl/carta/</t>
-        </is>
-      </c>
+          <t>9 6417 7736</t>
+        </is>
+      </c>
+      <c r="F12" t="inlineStr"/>
       <c r="G12" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante peruano</t>
         </is>
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurant+Zasha/@-36.6072718,-72.0992526,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d7d5eec972b7:0xfb0866f2c16242a9!8m2!3d-36.6072718!4d-72.0992526!16s%2Fg%2F11f54mczxm?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+3+Regiones/data=!4m7!3m6!1s0x9668d757623c17bb:0xf348bc1a5fa133b8!8m2!3d-36.6078265!4d-72.092205!16s%2Fg%2F11qbr9886l!19sChIJuxc8YlfXaJYRuDOhXxq8SPM?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-36.6072718</t>
+          <t>-36.6078265</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-72.0992526</t>
+          <t>-72.092205</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -1713,12 +1713,12 @@
       </c>
       <c r="O12" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P12" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q12" t="inlineStr">
@@ -1746,32 +1746,32 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>Restaurante La Motoneta</t>
+          <t>Vita Wines House, Casa de vinos</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>4.4</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>89</t>
+          <t>93</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>Km 7. ruta Termas de Chillán (N-55), Chillán, Ñuble</t>
+          <t>Los Mallines 208, 3800146 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
         <is>
-          <t>9 7148 0052</t>
+          <t>9 9933 2606</t>
         </is>
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>http://www.lamotoneta.cl/</t>
+          <t>https://vitawines.cl/</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -1781,17 +1781,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+La+Motoneta/data=!4m7!3m6!1s0x9669299c4b2bf56f:0xa1dd1bdc838da646!8m2!3d-36.6419948!4d-72.062745!16s%2Fg%2F11g9qvdn6g!19sChIJb_UrS5wpaZYRRqaNg9wb3aE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Vita+Wines+House,+Casa+de+vinos/data=!4m7!3m6!1s0x9668d786459af0b9:0xff81c3a3610f9d43!8m2!3d-36.5928329!4d-72.1037306!16s%2Fg%2F11k9zc5rwv!19sChIJufCaRYbXaJYRQ50PYaPDgf8?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-36.6419948</t>
+          <t>-36.5928329</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-72.062745</t>
+          <t>-72.1037306</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -1816,7 +1816,7 @@
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
@@ -1849,32 +1849,32 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>Restaurante El Faro</t>
+          <t>Volcano Restaurant</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>438</t>
+          <t>184</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>Claudio Arrau 185, 3820572 Chillán, Ñuble</t>
+          <t>Casino marina del sol - Variante Nahueltoro 251, local 2, 3820572 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
         <is>
-          <t>(42) 224 8409</t>
+          <t>9 5827 1755</t>
         </is>
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>http://elfarochillan.cl/</t>
+          <t>http://www.volcanorestaurant.cl/</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -1884,17 +1884,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+El+Faro/data=!4m7!3m6!1s0x9668d7d08707087b:0xa8c8a930456dfcb8!8m2!3d-36.6012984!4d-72.1053224!16s%2Fg%2F11yk5dlr5!19sChIJewgHh9DXaJYRuPxtRTCpyKg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Volcano+Restaurant/data=!4m7!3m6!1s0x9668d7ba06c77f91:0x6f3eb74ac17461d!8m2!3d-36.5609654!4d-72.0933011!16s%2Fg%2F11k56967tb!19sChIJkX_HBrrXaJYRHUYXrHTr8wY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-36.6012984</t>
+          <t>-36.5609654</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-72.1053224</t>
+          <t>-72.0933011</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -1919,7 +1919,7 @@
       </c>
       <c r="O14" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P14" t="inlineStr">
@@ -1952,34 +1952,30 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>Bar Prócer</t>
+          <t>Restaurant El Chapu</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>4.9</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>545</t>
+          <t>822</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>Casino Marina del Sol, 3780000 Chillán, Ñuble</t>
+          <t>Las Rosas 641, Chillán, Biobío</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
         <is>
-          <t>9 5206 6540</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>http://www.instagram.com/barprocer</t>
-        </is>
-      </c>
+          <t>9 9711 3623</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr"/>
       <c r="G15" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -1987,17 +1983,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Bar+Pr%C3%B3cer/data=!4m7!3m6!1s0x9668d7e46a1c3a9f:0xd4b92823219ba1d0!8m2!3d-36.5603212!4d-72.0933141!16s%2Fg%2F11r_xh1py5!19sChIJnzocauTXaJYR0KGbISMoudQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurant+El+Chapu/data=!4m7!3m6!1s0x9669ca19b111c019:0x70fd64e57055940c!8m2!3d-36.611892!4d-72.0821374!16s%2Fg%2F1tgwc36w!19sChIJGcARsRnKaZYRDJRVcOVk_XA?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-36.5603212</t>
+          <t>-36.611892</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-72.0933141</t>
+          <t>-72.0821374</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -2022,12 +2018,12 @@
       </c>
       <c r="O15" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P15" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q15" t="inlineStr">
@@ -2055,34 +2051,30 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>La Choza Restaurant Peruano</t>
+          <t>Restaurant Punto Limeño</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>60</t>
+          <t>66</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>Isabel Riquelme 15, 3800497 Chillán, Ñuble</t>
+          <t>Carrera 148, 3800469 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
         <is>
-          <t>(42) 223 4518</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>http://www.lachozarestaurant.cl/</t>
-        </is>
-      </c>
+          <t>9 5400 2625</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr"/>
       <c r="G16" t="inlineStr">
         <is>
           <t>Restaurante peruano</t>
@@ -2090,17 +2082,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Choza+Restaurant+Peruano/data=!4m7!3m6!1s0x9668d7d30a3e4625:0x7bc5361c4849aed4!8m2!3d-36.6011418!4d-72.0968693!16s%2Fg%2F11c1pgbphg!19sChIJJUY-CtPXaJYR1K5JSBw2xXs?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurant+Punto+Lime%C3%B1o/data=!4m7!3m6!1s0x9668d7df00000001:0x186a91f217b358e9!8m2!3d-36.6011131!4d-72.1038751!16s%2Fg%2F11c1x38b8j!19sChIJAQAAAN_XaJYR6VizF_KRahg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-36.6011418</t>
+          <t>-36.6011131</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-72.0968693</t>
+          <t>-72.1038751</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -2125,12 +2117,12 @@
       </c>
       <c r="O16" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P16" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q16" t="inlineStr">
@@ -2158,34 +2150,30 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>Kuranepe Restaurante</t>
+          <t>Restaurante Sabor a Mar</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>430</t>
+          <t>291</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>Longitudinal norte 420, 3800043 Chillán, Ñuble</t>
+          <t>Francia 207, 3801057 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
         <is>
-          <t>(42) 227 1419</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>https://www.facebook.com/Kuraneperestauranteoficial/</t>
-        </is>
-      </c>
+          <t>(42) 232 8905</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr"/>
       <c r="G17" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2193,17 +2181,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Kuranepe+Restaurante/@-36.5936079,-72.10458,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d7cf4a03463b:0xa8f50977d8bae1a5!8m2!3d-36.5936079!4d-72.10458!16s%2Fg%2F11fx7vrwgg?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+Sabor+a+Mar/data=!4m7!3m6!1s0x9668d7ce40d1aee7:0xcc4e547731967766!8m2!3d-36.5967373!4d-72.1019622!16s%2Fg%2F11c67qwdz6!19sChIJ567RQM7XaJYRZneWMXdUTsw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-36.5936079</t>
+          <t>-36.5967373</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-72.10458</t>
+          <t>-72.1019622</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -2228,12 +2216,12 @@
       </c>
       <c r="O17" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P17" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q17" t="inlineStr">
@@ -2261,34 +2249,30 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>La Cabaña Sándwich</t>
+          <t>Restaurante "Rocas"</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>972</t>
+          <t>484</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>Av. Argentina 584, 3800851 Chillán, Ñuble</t>
+          <t>Av. Libertad 684, Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
         <is>
-          <t>9 8344 6550</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>https://m.facebook.com/cabanasandwich</t>
-        </is>
-      </c>
+          <t>9 4188 5321</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr"/>
       <c r="G18" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2296,17 +2280,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/La+Caba%C3%B1a+S%C3%A1ndwich/data=!4m7!3m6!1s0x966929d4d3e5821b:0x8e58af11e8503f06!8m2!3d-36.6101982!4d-72.0940185!16s%2Fg%2F11f1v2p3wj!19sChIJG4Ll09QpaZYRBj9Q6BGvWI4?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+%22Rocas%22/data=!4m7!3m6!1s0x9668d779cbadee3f:0x7c331be78e0b9dd1!8m2!3d-36.6067519!4d-72.1011348!16s%2Fg%2F11h2jmqsjv!19sChIJP-6ty3nXaJYR0Z0LjucbM3w?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-36.6101982</t>
+          <t>-36.6067519</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-72.0940185</t>
+          <t>-72.1011348</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -2331,12 +2315,12 @@
       </c>
       <c r="O18" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P18" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q18" t="inlineStr">
@@ -2359,41 +2343,37 @@
       <c r="AD18" t="inlineStr"/>
       <c r="AE18" t="inlineStr"/>
       <c r="AF18" t="inlineStr"/>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>Revisar: parece sandwich</t>
-        </is>
-      </c>
+      <c r="AG18" t="inlineStr"/>
     </row>
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>Secretos de la Nona Chillán Casa Matriz Tienda 1</t>
+          <t>Restaurante La Motoneta</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.4</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>717</t>
+          <t>90</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>Arauco 937, 3800926 Chillán, Ñuble</t>
+          <t>Km 7. ruta Termas de Chillán (N-55), Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
         <is>
-          <t>9 8573 2009</t>
+          <t>9 7148 0052</t>
         </is>
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>https://secretosdelanona.cl/</t>
+          <t>http://www.lamotoneta.cl/</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -2403,17 +2383,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Secretos+de+la+Nona+Chill%C3%A1n+Casa+Matriz+Tienda+1/@-36.6116984,-72.1043029,17z/data=!3m1!4b1!4m6!3m5!1s0x96692828f5997465:0x8416716d711296f7!8m2!3d-36.6116984!4d-72.1043029!16s%2Fg%2F11bwqg83gz?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+La+Motoneta/data=!4m7!3m6!1s0x9669299c4b2bf56f:0xa1dd1bdc838da646!8m2!3d-36.6419948!4d-72.062745!16s%2Fg%2F11g9qvdn6g!19sChIJb_UrS5wpaZYRRqaNg9wb3aE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-36.6116984</t>
+          <t>-36.6419948</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-72.1043029</t>
+          <t>-72.062745</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -2438,7 +2418,7 @@
       </c>
       <c r="O19" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P19" t="inlineStr">
@@ -2471,30 +2451,34 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>Brote de Primavera</t>
+          <t>Bar Prócer</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.9</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>140</t>
+          <t>545</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>Arturo Prat 415, 3780000 Chillán, Bío Bío</t>
+          <t>Casino Marina del Sol, 3780000 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
         <is>
-          <t>9 4855 5636</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr"/>
+          <t>9 5206 6540</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>http://www.instagram.com/barprocer</t>
+        </is>
+      </c>
       <c r="G20" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2502,17 +2486,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Brote+de+Primavera/@-36.610358,-72.1070076,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d743b1787749:0x74379625a16cd3fe!8m2!3d-36.610358!4d-72.1070076!16s%2Fg%2F11qyc3f_dy?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Bar+Pr%C3%B3cer/data=!4m7!3m6!1s0x9668d7e46a1c3a9f:0xd4b92823219ba1d0!8m2!3d-36.5603212!4d-72.0933141!16s%2Fg%2F11r_xh1py5!19sChIJnzocauTXaJYR0KGbISMoudQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-36.610358</t>
+          <t>-36.5603212</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-72.1070076</t>
+          <t>-72.0933141</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -2537,12 +2521,12 @@
       </c>
       <c r="O20" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P20" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q20" t="inlineStr">
@@ -2570,30 +2554,34 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>Restaurante Huasi del Inca</t>
+          <t>Restaurante El Faro</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>4.5</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>98</t>
+          <t>438</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>Av. Libertad 779, 3800693 Chillán, Ñuble</t>
+          <t>Claudio Arrau 185, 3820572 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
         <is>
-          <t>9 6492 8078</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr"/>
+          <t>(42) 224 8409</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>http://elfarochillan.cl/</t>
+        </is>
+      </c>
       <c r="G21" t="inlineStr">
         <is>
           <t>Restaurante</t>
@@ -2601,17 +2589,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+Huasi+del+Inca/data=!4m7!3m6!1s0x9668d706035fa13d:0xe290519111abb910!8m2!3d-36.6068085!4d-72.0995556!16s%2Fg%2F11tjhq6knq!19sChIJPaFfAwbXaJYRELmrEZFRkOI?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Restaurante+El+Faro/data=!4m7!3m6!1s0x9668d7d08707087b:0xa8c8a930456dfcb8!8m2!3d-36.6012984!4d-72.1053224!16s%2Fg%2F11yk5dlr5!19sChIJewgHh9DXaJYRuPxtRTCpyKg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-36.6068085</t>
+          <t>-36.6012984</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-72.0995556</t>
+          <t>-72.1053224</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -2636,12 +2624,12 @@
       </c>
       <c r="O21" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P21" t="inlineStr">
         <is>
-          <t>Parcial</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q21" t="inlineStr">
@@ -2669,48 +2657,44 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>Casona Villablanca</t>
+          <t>Casa Pierrot</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>4.2</t>
+          <t>4.6</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>177</t>
+          <t>149</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>Baquedano 1085, 3820489 Chillán Viejo, Ñuble</t>
+          <t>Cocharcas 786, 3800990 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E22" t="inlineStr"/>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>https://www.instagram.com/casona_villablanca/</t>
-        </is>
-      </c>
+      <c r="F22" t="inlineStr"/>
       <c r="G22" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante italiano</t>
         </is>
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casona+Villablanca/data=!4m7!3m6!1s0x966929654d71af3b:0xa6f81422452bf72d!8m2!3d-36.6326317!4d-72.1255024!16s%2Fg%2F11rq467bb9!19sChIJO69xTWUpaZYRLfcrRSIU-KY?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Casa+Pierrot/data=!4m7!3m6!1s0x96692900415732a3:0x3d2904724e7faefc!8m2!3d-36.6131455!4d-72.1019494!16s%2Fg%2F11vr187ltd!19sChIJozJXQQApaZYR_K5_TnIEKT0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-36.6326317</t>
+          <t>-36.6131455</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-72.1255024</t>
+          <t>-72.1019494</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -2735,7 +2719,7 @@
       </c>
       <c r="O22" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P22" t="inlineStr">
@@ -2772,32 +2756,32 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>Sushi Ryge Chillán</t>
+          <t>Mesón de Ñeko Collín</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>4.7</t>
+          <t>4.2</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>273</t>
+          <t>767</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>Arauco 861, local 103, 3780000 Chillán, Ñuble</t>
+          <t>Av. Collín 1005, 3790068 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
         <is>
-          <t>(2) 2214 1534</t>
+          <t>(42) 232 3646</t>
         </is>
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>https://www.ryge.cl/</t>
+          <t>https://www.facebook.com/mesondeneko/</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -2807,17 +2791,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Sushi+Ryge+Chill%C3%A1n/@-36.6107928,-72.1035736,17z/data=!3m1!4b1!4m6!3m5!1s0x966929d8d05a5faf:0x7f750009ff92d948!8m2!3d-36.6107928!4d-72.1035736!16s%2Fg%2F11yb7m828n?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Mes%C3%B3n+de+%C3%91eko+Coll%C3%ADn/data=!4m7!3m6!1s0x9669282dcc494ddd:0x14098979cdd5984c!8m2!3d-36.6163254!4d-72.0993197!16s%2Fg%2F11c2nbrxm1!19sChIJ3U1JzC0oaZYRTJjVzXmJCRQ?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-36.6107928</t>
+          <t>-36.6163254</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-72.1035736</t>
+          <t>-72.0993197</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -2842,7 +2826,7 @@
       </c>
       <c r="O23" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P23" t="inlineStr">
@@ -2906,7 +2890,7 @@
       </c>
       <c r="H24" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Restaurante+El+Fara%C3%B3n+Comida+%C3%81rabe/@-36.6165257,-72.0962917,17z/data=!3m1!4b1!4m6!3m5!1s0x96692900287adec7:0xb9d717b7f3d051ac!8m2!3d-36.6165257!4d-72.0962917!16s%2Fg%2F11y3yrq3jk?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Restaurante+El+Fara%C3%B3n+Comida+%C3%81rabe/data=!4m7!3m6!1s0x96692900287adec7:0xb9d717b7f3d051ac!8m2!3d-36.6165257!4d-72.0962917!16s%2Fg%2F11y3yrq3jk!19sChIJx956KAApaZYRrFHQ87cX17k?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I24" t="inlineStr">
@@ -2941,7 +2925,7 @@
       </c>
       <c r="O24" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P24" t="inlineStr">
@@ -2974,44 +2958,52 @@
     <row r="25">
       <c r="A25" t="inlineStr">
         <is>
-          <t>Casa Pierrot</t>
+          <t>Kuranepe Restaurante</t>
         </is>
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>4.6</t>
+          <t>4.3</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>149</t>
+          <t>430</t>
         </is>
       </c>
       <c r="D25" t="inlineStr">
         <is>
-          <t>Cocharcas 786, 3800990 Chillán, Ñuble</t>
-        </is>
-      </c>
-      <c r="E25" t="inlineStr"/>
-      <c r="F25" t="inlineStr"/>
+          <t>Longitudinal norte 420, 3800043 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E25" t="inlineStr">
+        <is>
+          <t>(42) 227 1419</t>
+        </is>
+      </c>
+      <c r="F25" t="inlineStr">
+        <is>
+          <t>https://www.facebook.com/Kuraneperestauranteoficial/</t>
+        </is>
+      </c>
       <c r="G25" t="inlineStr">
         <is>
-          <t>Restaurante italiano</t>
+          <t>Restaurante</t>
         </is>
       </c>
       <c r="H25" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Casa+Pierrot/data=!4m7!3m6!1s0x96692900415732a3:0x3d2904724e7faefc!8m2!3d-36.6131455!4d-72.1019494!16s%2Fg%2F11vr187ltd!19sChIJozJXQQApaZYR_K5_TnIEKT0?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+          <t>https://www.google.com/maps/place/Kuranepe+Restaurante/data=!4m7!3m6!1s0x9668d7cf4a03463b:0xa8f50977d8bae1a5!8m2!3d-36.5936079!4d-72.10458!16s%2Fg%2F11fx7vrwgg!19sChIJO0YDSs_XaJYRpeG62HcJ9ag?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I25" t="inlineStr">
         <is>
-          <t>-36.6131455</t>
+          <t>-36.5936079</t>
         </is>
       </c>
       <c r="J25" t="inlineStr">
         <is>
-          <t>-72.1019494</t>
+          <t>-72.10458</t>
         </is>
       </c>
       <c r="K25" t="inlineStr">
@@ -3036,12 +3028,12 @@
       </c>
       <c r="O25" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P25" t="inlineStr">
         <is>
-          <t>Sin teléfono</t>
+          <t>Completo</t>
         </is>
       </c>
       <c r="Q25" t="inlineStr">
@@ -3064,61 +3056,53 @@
       <c r="AD25" t="inlineStr"/>
       <c r="AE25" t="inlineStr"/>
       <c r="AF25" t="inlineStr"/>
-      <c r="AG25" t="inlineStr">
-        <is>
-          <t>Sin teléfono visible</t>
-        </is>
-      </c>
+      <c r="AG25" t="inlineStr"/>
     </row>
     <row r="26">
       <c r="A26" t="inlineStr">
         <is>
-          <t>Texas Restaurant</t>
+          <t>Tartara’s Food</t>
         </is>
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>4.3</t>
+          <t>4.8</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>542</t>
+          <t>12</t>
         </is>
       </c>
       <c r="D26" t="inlineStr">
         <is>
-          <t>Isabel Riquelme 580, 3780000 Chillán, Ñuble</t>
+          <t>Av. Collín 817, 3780000 Chillán, Ñuble</t>
         </is>
       </c>
       <c r="E26" t="inlineStr">
         <is>
-          <t>9 3359 2094</t>
-        </is>
-      </c>
-      <c r="F26" t="inlineStr">
-        <is>
-          <t>https://sites.google.com/texasrestaurant.cl/texasrestaurant/inicio</t>
-        </is>
-      </c>
+          <t>9 2254 0717</t>
+        </is>
+      </c>
+      <c r="F26" t="inlineStr"/>
       <c r="G26" t="inlineStr">
         <is>
-          <t>Restaurante</t>
+          <t>Restaurante familiar</t>
         </is>
       </c>
       <c r="H26" t="inlineStr">
         <is>
-          <t>https://www.google.com/maps/place/Texas+Restaurant/@-36.6078455,-72.0998168,17z/data=!3m1!4b1!4m6!3m5!1s0x9668d7d5f8d8e8e7:0xa94ba176a177cc8a!8m2!3d-36.6078455!4d-72.0998168!16s%2Fg%2F11c618fx9b?authuser=0&amp;hl=es-419&amp;entry=ttu&amp;g_ep=EgoyMDI2MDUyMC4wIKXMDSoASAFQAw%3D%3D</t>
+          <t>https://www.google.com/maps/place/Tartara%E2%80%99s+Food/data=!4m7!3m6!1s0x966929d1f8fa9f1f:0x486f85247a3365e2!8m2!3d-36.6155259!4d-72.1020643!16s%2Fg%2F11kblvngwx!19sChIJH5_6-NEpaZYR4mUzeiSFb0g?authuser=0&amp;hl=es-419&amp;rclk=1</t>
         </is>
       </c>
       <c r="I26" t="inlineStr">
         <is>
-          <t>-36.6078455</t>
+          <t>-36.6155259</t>
         </is>
       </c>
       <c r="J26" t="inlineStr">
         <is>
-          <t>-72.0998168</t>
+          <t>-72.1020643</t>
         </is>
       </c>
       <c r="K26" t="inlineStr">
@@ -3143,12 +3127,12 @@
       </c>
       <c r="O26" t="inlineStr">
         <is>
-          <t>2026-05-24</t>
+          <t>2026-05-25</t>
         </is>
       </c>
       <c r="P26" t="inlineStr">
         <is>
-          <t>Completo</t>
+          <t>Parcial</t>
         </is>
       </c>
       <c r="Q26" t="inlineStr">
@@ -3173,8 +3157,515 @@
       <c r="AF26" t="inlineStr"/>
       <c r="AG26" t="inlineStr"/>
     </row>
+    <row r="27">
+      <c r="A27" t="inlineStr">
+        <is>
+          <t>Restaurante Entre Chillán Y Chillán Viejo</t>
+        </is>
+      </c>
+      <c r="B27" t="inlineStr">
+        <is>
+          <t>4.2</t>
+        </is>
+      </c>
+      <c r="C27" t="inlineStr">
+        <is>
+          <t>81</t>
+        </is>
+      </c>
+      <c r="D27" t="inlineStr">
+        <is>
+          <t>Tegualda 11-129, 3790287 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E27" t="inlineStr">
+        <is>
+          <t>9 9447 9148</t>
+        </is>
+      </c>
+      <c r="F27" t="inlineStr"/>
+      <c r="G27" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H27" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Restaurante+Entre+Chill%C3%A1n+Y+Chill%C3%A1n+Viejo/data=!4m7!3m6!1s0x96692819cb16975f:0xc48ff1ace347cf0a!8m2!3d-36.620945!4d-72.1209983!16s%2Fg%2F11c0qgzsyw!19sChIJX5cWyxkoaZYRCs9H46zxj8Q?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I27" t="inlineStr">
+        <is>
+          <t>-36.620945</t>
+        </is>
+      </c>
+      <c r="J27" t="inlineStr">
+        <is>
+          <t>-72.1209983</t>
+        </is>
+      </c>
+      <c r="K27" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="L27" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="M27" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N27" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O27" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P27" t="inlineStr">
+        <is>
+          <t>Parcial</t>
+        </is>
+      </c>
+      <c r="Q27" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R27" t="inlineStr"/>
+      <c r="S27" t="inlineStr"/>
+      <c r="T27" t="inlineStr"/>
+      <c r="U27" t="inlineStr"/>
+      <c r="V27" t="inlineStr"/>
+      <c r="W27" t="inlineStr"/>
+      <c r="X27" t="inlineStr"/>
+      <c r="Y27" t="inlineStr"/>
+      <c r="Z27" t="inlineStr"/>
+      <c r="AA27" t="inlineStr"/>
+      <c r="AB27" t="inlineStr"/>
+      <c r="AC27" t="inlineStr"/>
+      <c r="AD27" t="inlineStr"/>
+      <c r="AE27" t="inlineStr"/>
+      <c r="AF27" t="inlineStr"/>
+      <c r="AG27" t="inlineStr"/>
+    </row>
+    <row r="28">
+      <c r="A28" t="inlineStr">
+        <is>
+          <t>Andén Bistro Tapas</t>
+        </is>
+      </c>
+      <c r="B28" t="inlineStr">
+        <is>
+          <t>4.6</t>
+        </is>
+      </c>
+      <c r="C28" t="inlineStr">
+        <is>
+          <t>89</t>
+        </is>
+      </c>
+      <c r="D28" t="inlineStr">
+        <is>
+          <t>Camino Colonia Bernardo O'Higgins 1572, 3820572 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E28" t="inlineStr">
+        <is>
+          <t>9 4274 3882</t>
+        </is>
+      </c>
+      <c r="F28" t="inlineStr">
+        <is>
+          <t>https://instagram.com/anden_bistrotapas?igshid=MzRlODBiNWFlZA==</t>
+        </is>
+      </c>
+      <c r="G28" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H28" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/And%C3%A9n+Bistro+Tapas/data=!4m7!3m6!1s0x9668d7139fd96775:0x314731108e164203!8m2!3d-36.5867085!4d-72.0760796!16s%2Fg%2F11stp3xpmx!19sChIJdWfZnxPXaJYRA0IWjhAxRzE?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I28" t="inlineStr">
+        <is>
+          <t>-36.5867085</t>
+        </is>
+      </c>
+      <c r="J28" t="inlineStr">
+        <is>
+          <t>-72.0760796</t>
+        </is>
+      </c>
+      <c r="K28" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="L28" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="M28" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N28" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O28" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P28" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q28" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R28" t="inlineStr"/>
+      <c r="S28" t="inlineStr"/>
+      <c r="T28" t="inlineStr"/>
+      <c r="U28" t="inlineStr"/>
+      <c r="V28" t="inlineStr"/>
+      <c r="W28" t="inlineStr"/>
+      <c r="X28" t="inlineStr"/>
+      <c r="Y28" t="inlineStr"/>
+      <c r="Z28" t="inlineStr"/>
+      <c r="AA28" t="inlineStr"/>
+      <c r="AB28" t="inlineStr"/>
+      <c r="AC28" t="inlineStr"/>
+      <c r="AD28" t="inlineStr"/>
+      <c r="AE28" t="inlineStr"/>
+      <c r="AF28" t="inlineStr"/>
+      <c r="AG28" t="inlineStr"/>
+    </row>
+    <row r="29">
+      <c r="A29" t="inlineStr">
+        <is>
+          <t>Cassis Mall Arauco Chillán</t>
+        </is>
+      </c>
+      <c r="B29" t="inlineStr">
+        <is>
+          <t>4.7</t>
+        </is>
+      </c>
+      <c r="C29" t="inlineStr">
+        <is>
+          <t>172</t>
+        </is>
+      </c>
+      <c r="D29" t="inlineStr">
+        <is>
+          <t>El Roble 770, Local 14, piso 1, 3800846 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E29" t="inlineStr">
+        <is>
+          <t>9 3400 7643</t>
+        </is>
+      </c>
+      <c r="F29" t="inlineStr">
+        <is>
+          <t>https://cassiscafe.com/</t>
+        </is>
+      </c>
+      <c r="G29" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H29" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Cassis+Mall+Arauco+Chill%C3%A1n/data=!4m7!3m6!1s0x9669291a45c5f073:0x7c6e5e884dd1b012!8m2!3d-36.60968!4d-72.1009!16s%2Fg%2F11wr2vrt08!19sChIJc_DFRRopaZYRErDRTYhebnw?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I29" t="inlineStr">
+        <is>
+          <t>-36.60968</t>
+        </is>
+      </c>
+      <c r="J29" t="inlineStr">
+        <is>
+          <t>-72.1009</t>
+        </is>
+      </c>
+      <c r="K29" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="L29" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="M29" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N29" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O29" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P29" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q29" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R29" t="inlineStr"/>
+      <c r="S29" t="inlineStr"/>
+      <c r="T29" t="inlineStr"/>
+      <c r="U29" t="inlineStr"/>
+      <c r="V29" t="inlineStr"/>
+      <c r="W29" t="inlineStr"/>
+      <c r="X29" t="inlineStr"/>
+      <c r="Y29" t="inlineStr"/>
+      <c r="Z29" t="inlineStr"/>
+      <c r="AA29" t="inlineStr"/>
+      <c r="AB29" t="inlineStr"/>
+      <c r="AC29" t="inlineStr"/>
+      <c r="AD29" t="inlineStr"/>
+      <c r="AE29" t="inlineStr"/>
+      <c r="AF29" t="inlineStr"/>
+      <c r="AG29" t="inlineStr"/>
+    </row>
+    <row r="30">
+      <c r="A30" t="inlineStr">
+        <is>
+          <t>Ficus Restaurante</t>
+        </is>
+      </c>
+      <c r="B30" t="inlineStr">
+        <is>
+          <t>4.4</t>
+        </is>
+      </c>
+      <c r="C30" t="inlineStr">
+        <is>
+          <t>97</t>
+        </is>
+      </c>
+      <c r="D30" t="inlineStr">
+        <is>
+          <t>Rosas 392, 3800538 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E30" t="inlineStr">
+        <is>
+          <t>(42) 221 2176</t>
+        </is>
+      </c>
+      <c r="F30" t="inlineStr">
+        <is>
+          <t>http://www.ficuschillan.com/</t>
+        </is>
+      </c>
+      <c r="G30" t="inlineStr">
+        <is>
+          <t>Pizza para llevar</t>
+        </is>
+      </c>
+      <c r="H30" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Ficus+Restaurante/data=!4m7!3m6!1s0x9668d7dbb6df605f:0xc82caea297245715!8m2!3d-36.603014!4d-72.109585!16s%2Fg%2F1v75t3d9!19sChIJX2DfttvXaJYRFVckl6KuLMg?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I30" t="inlineStr">
+        <is>
+          <t>-36.603014</t>
+        </is>
+      </c>
+      <c r="J30" t="inlineStr">
+        <is>
+          <t>-72.109585</t>
+        </is>
+      </c>
+      <c r="K30" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="L30" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="M30" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N30" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O30" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P30" t="inlineStr">
+        <is>
+          <t>Completo</t>
+        </is>
+      </c>
+      <c r="Q30" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R30" t="inlineStr"/>
+      <c r="S30" t="inlineStr"/>
+      <c r="T30" t="inlineStr"/>
+      <c r="U30" t="inlineStr"/>
+      <c r="V30" t="inlineStr"/>
+      <c r="W30" t="inlineStr"/>
+      <c r="X30" t="inlineStr"/>
+      <c r="Y30" t="inlineStr"/>
+      <c r="Z30" t="inlineStr"/>
+      <c r="AA30" t="inlineStr"/>
+      <c r="AB30" t="inlineStr"/>
+      <c r="AC30" t="inlineStr"/>
+      <c r="AD30" t="inlineStr"/>
+      <c r="AE30" t="inlineStr"/>
+      <c r="AF30" t="inlineStr"/>
+      <c r="AG30" t="inlineStr"/>
+    </row>
+    <row r="31">
+      <c r="A31" t="inlineStr">
+        <is>
+          <t>Troya Restaurant</t>
+        </is>
+      </c>
+      <c r="B31" t="inlineStr">
+        <is>
+          <t>4.3</t>
+        </is>
+      </c>
+      <c r="C31" t="inlineStr">
+        <is>
+          <t>78</t>
+        </is>
+      </c>
+      <c r="D31" t="inlineStr">
+        <is>
+          <t>Camino a cato - km 1.8, 3820572 Chillán, Ñuble</t>
+        </is>
+      </c>
+      <c r="E31" t="inlineStr"/>
+      <c r="F31" t="inlineStr"/>
+      <c r="G31" t="inlineStr">
+        <is>
+          <t>Restaurante</t>
+        </is>
+      </c>
+      <c r="H31" t="inlineStr">
+        <is>
+          <t>https://www.google.com/maps/place/Troya+Restaurant/data=!4m7!3m6!1s0x9668d7dbc86275c3:0x8bbbd2399dc2d8a5!8m2!3d-36.5735557!4d-72.0518263!16s%2Fg%2F11tjqmm4lv!19sChIJw3ViyNvXaJYRpdjCnTnSu4s?authuser=0&amp;hl=es-419&amp;rclk=1</t>
+        </is>
+      </c>
+      <c r="I31" t="inlineStr">
+        <is>
+          <t>-36.5735557</t>
+        </is>
+      </c>
+      <c r="J31" t="inlineStr">
+        <is>
+          <t>-72.0518263</t>
+        </is>
+      </c>
+      <c r="K31" t="inlineStr">
+        <is>
+          <t>Chillán</t>
+        </is>
+      </c>
+      <c r="L31" t="inlineStr">
+        <is>
+          <t>Ñuble</t>
+        </is>
+      </c>
+      <c r="M31" t="inlineStr">
+        <is>
+          <t>Chile</t>
+        </is>
+      </c>
+      <c r="N31" t="inlineStr">
+        <is>
+          <t>Google Maps web scraping con Playwright</t>
+        </is>
+      </c>
+      <c r="O31" t="inlineStr">
+        <is>
+          <t>2026-05-25</t>
+        </is>
+      </c>
+      <c r="P31" t="inlineStr">
+        <is>
+          <t>Sin teléfono</t>
+        </is>
+      </c>
+      <c r="Q31" t="inlineStr">
+        <is>
+          <t>Sí</t>
+        </is>
+      </c>
+      <c r="R31" t="inlineStr"/>
+      <c r="S31" t="inlineStr"/>
+      <c r="T31" t="inlineStr"/>
+      <c r="U31" t="inlineStr"/>
+      <c r="V31" t="inlineStr"/>
+      <c r="W31" t="inlineStr"/>
+      <c r="X31" t="inlineStr"/>
+      <c r="Y31" t="inlineStr"/>
+      <c r="Z31" t="inlineStr"/>
+      <c r="AA31" t="inlineStr"/>
+      <c r="AB31" t="inlineStr"/>
+      <c r="AC31" t="inlineStr"/>
+      <c r="AD31" t="inlineStr"/>
+      <c r="AE31" t="inlineStr"/>
+      <c r="AF31" t="inlineStr"/>
+      <c r="AG31" t="inlineStr">
+        <is>
+          <t>Sin teléfono visible</t>
+        </is>
+      </c>
+    </row>
   </sheetData>
-  <autoFilter ref="A1:AG26"/>
+  <autoFilter ref="A1:AG31"/>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>